--- a/output/results.xlsx
+++ b/output/results.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,6 +25,7 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font/>
   </fonts>
   <fills count="2">
     <fill>
@@ -34,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,15 +43,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="text_style" xfId="1" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -464,188 +469,188 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Rampura Mota</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>34576</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>08/01/2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>IORA/31/02/112/9/2026</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>838/2023</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>16888</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>28/05/2023</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Rampura Mota</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>251/p2</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>5997.00</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>16/02/2026</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>IORA/31/02/112/25/2026</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>141/2026</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>04047</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>21/01/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Rampura Mota</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>16510</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>IORA/31/02/112/8/2026</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>851/2025</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>16959</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>23/05/2025</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Rampura Mota</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>16534</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>IORA/31/02/112/7/2026</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>837/2025</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>16792</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>28/05/2025</t>
         </is>
